--- a/data/anggota.xlsx
+++ b/data/anggota.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -630,6 +630,72 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>a75fcc53-0fb0-4957-b0ff-694a1bfc40c0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AGT-0005</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>88888888</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AGT-15612551561</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AGT-0006</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9999999999</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>hayuk</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>jalanin aja dulu</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anggota.xlsx
+++ b/data/anggota.xlsx
@@ -417,14 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -481,37 +481,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9b6a5ab2-720d-4c05-bb25-0b8629c85dd3</t>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGT-0001</t>
+          <t>AGT-020</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7984563124567</v>
+        <v>1234567891234560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>boseng</t>
+          <t>Siti Aulia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>babakan caringin</t>
+          <t>Bandung</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8465132978</v>
+        <v>81298765432</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -520,179 +520,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>582f9a5f-a0c9-4737-a724-1fd6f9307798</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AGT-0002</t>
-        </is>
+          <t>4f928756-def0-4214-beb7-4c037ed920cf</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>123</v>
       </c>
       <c r="C3" t="n">
-        <v>963852741123</v>
+        <v>1111111111111111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>shidqi</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cikapundung</t>
+          <t>wqswwsw</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87946513281</v>
+        <v>81298765432</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>20000000</v>
+        <v>252</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AGT-0003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AGT-0003</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>789123456</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>jamang</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>cikapundung</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AGT-000988</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AGT-0004</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>789123456</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>hikmal</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>cikapundung</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>a75fcc53-0fb0-4957-b0ff-694a1bfc40c0</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AGT-0005</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>88888888</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AGT-15612551561</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AGT-0006</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>9999999999</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>hayuk</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>jalanin aja dulu</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/anggota.xlsx
+++ b/data/anggota.xlsx
@@ -417,18 +417,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,88 +472,127 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>no_rekening</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>nama_bank</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>penghasilan_bersih</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>cicilan_lain</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>simpanan_pokok</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1234567891234560</v>
+        <v>3204298796411532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bandung</t>
+          <t>ciparay</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>81298765432</v>
+        <v>81697456122</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="I2" t="n">
+        <v>9638527411234568</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BNI</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4f928756-def0-4214-beb7-4c037ed920cf</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>123</v>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>1111111111111111</v>
+        <v>1234567890123456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Septiawan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>wqswwsw</t>
+          <t>Bandung</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>81298765432</v>
+        <v>8111111111111</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>252</v>
-      </c>
-      <c r="I3" t="n">
+        <v>322222222222222</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BNI</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/anggota.xlsx
+++ b/data/anggota.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -596,6 +596,90 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02b98d05-e120-42e8-81b2-1fe8887d5c70</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AG0001</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3174120101010001</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Budi Santoso</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>81234567890</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0618aeab-d75c-487e-b4cb-e99b9609ef46</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AG0002</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3273010202020002</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bandung</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>81298765432</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anggota.xlsx
+++ b/data/anggota.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
@@ -499,186 +499,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+          <t>AGT-DEMO-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGT-065</t>
+          <t>KOP-0001</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3204298796411532</v>
+        <v>3273000000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Boseng</t>
+          <t>Anggota Demo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ciparay</t>
+          <t>Bandung</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>81697456122</v>
+        <v>81200000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9638527411234568</v>
+        <v>111222333</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BNI</t>
+          <t>BCA</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>150000000</v>
+        <v>6500000</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1234567890123456</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Septiawan</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Bandung</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>8111111111111</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>322222222222222</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>BNI</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>150000000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>02b98d05-e120-42e8-81b2-1fe8887d5c70</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AG0001</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3174120101010001</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Budi Santoso</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Jakarta</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>81234567890</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>0618aeab-d75c-487e-b4cb-e99b9609ef46</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AG0002</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3273010202020002</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Siti Aulia</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bandung</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>81298765432</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>250000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/anggota.xlsx
+++ b/data/anggota.xlsx
@@ -417,21 +417,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,47 +457,72 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>nama</t>
+          <t>nama_lengkap</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>no_hp</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>alamat</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>no_telp</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>kategori_anggota</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tgl_bergabung</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>status_anggota</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>status_kredit</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>no_rekening</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>nama_bank</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>penghasilan_bersih</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>cicilan_lain</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>simpanan_pokok</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>foto_ktp</t>
         </is>
       </c>
     </row>
@@ -510,41 +540,40 @@
       <c r="C2" t="n">
         <v>3204298796411532</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Boseng</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>aaa</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>81697456122</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
         <v>9638527411234568</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>BNI</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
         <v>150000000</v>
       </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>500000</v>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,41 +589,40 @@
       <c r="C3" t="n">
         <v>3273000000000001</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Anggota Demo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Bandung</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>81200000001</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
         <v>111222333</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="N3" t="n">
         <v>6500000</v>
       </c>
-      <c r="K3" t="n">
+      <c r="O3" t="n">
         <v>500000</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>250000</v>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/anggota.xlsx
+++ b/data/anggota.xlsx
@@ -417,26 +417,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,30 +498,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>catatan_kredit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>no_rekening</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>nama_bank</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>penghasilan_bersih</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>cicilan_lain</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>simpanan_pokok</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>foto_ktp</t>
         </is>
@@ -529,7 +535,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+          <t>7afc9502-af5e-4bf3-b468-6375c7569652</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -538,91 +544,65 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3204298796411532</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>3207894561237894</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>boseng@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>816465123789</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>aaa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Rancabogo</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PNS</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>9638527411234568</v>
-      </c>
-      <c r="M2" t="inlineStr">
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Lancar</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>7.894561237894562e+16</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>BNI</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>150000000</v>
-      </c>
       <c r="O2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>500000</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AGT-DEMO-001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>KOP-0001</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3273000000000001</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Bandung</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>111222333</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>BCA</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>500000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>250000</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
